--- a/西友若菜_CKマスタ登録/CKマスタ登録フロー_比較表.xlsx
+++ b/西友若菜_CKマスタ登録/CKマスタ登録フロー_比較表.xlsx
@@ -838,7 +838,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>出典：元資料「CKマスタ登録フロー」シート＝西友 現状／「TOBE (製造)」シート＝トライアル導入後（新商談マスタ）</t>
+          <t>出典：元資料「CKマスタ登録フロー (現行)」シート＝西友 現状／「TOBE (製造)」シート＝トライアル導入後（新商談マスタ）</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="84" customHeight="1">
+    <row r="8" ht="98" customHeight="1">
       <c r="B8" s="7" t="n">
         <v>2</v>
       </c>
@@ -975,7 +975,7 @@
       <c r="F8" s="11" t="inlineStr">
         <is>
           <t>【登録チーム】原材料登録（eBASE・商談システム）
-　→ eBASE：原材料登録
+　※eBASEと商談システムに登録チームが同時に入力
 　→ 商談システム：原材料マスタ登録
 　　【承認ルート】品管 ⇒ 商品部本部長</t>
         </is>
@@ -990,7 +990,7 @@
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>登録先が「商談システム」→「新商談マスタ」に変わる。承認ルート（品管⇒本部長）がどうなるか未定</t>
+          <t>1回の登録（eBASE・商談システム同時）が「eBASE登録 → 新商談マスタ登録」の2段階に分かれる。登録先が商談システム→新商談マスタに変わり、承認ルート（品管⇒本部長）は未定</t>
         </is>
       </c>
       <c r="I8" s="15" t="inlineStr">
@@ -1006,7 +1006,7 @@
       <c r="K8" s="13" t="inlineStr">
         <is>
           <t>・新商談マスタでの承認ルート（品管⇒本部長を残すか）
-・eBASEと新商談マスタは二重入力か、自動連携か</t>
+・eBASE登録後、新商談マスタへは手入力か自動連携か</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>【本部品管】商談マスタの原材料コード と eBASEコードを紐付け
+          <t>【本部品管】eBASE上で、商談マスタの原材料コード と eBASEコードを紐付け
 （メーカーのeBASE作成＋原材料マスタ承認 の両方を受けて実施）</t>
         </is>
       </c>
@@ -1084,7 +1084,7 @@
         <is>
           <t>【登録チーム】中間品登録（eBASE・商談システム）
 　← 原材料登録完了 ＋ 商品規格書（商品開発）
-　→ eBASE：中間品登録
+　※eBASEと商談システムに同時に入力
 　→ 商談システム：中間品マスタ登録
 　　【承認ルート】品管 ⇒ 商品部本部長</t>
         </is>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>前工程（原材料→中間品）のつながりは同じ。登録先が新商談マスタに変わり、承認ルートが未定</t>
+          <t>前工程（原材料→中間品）のつながりは同じ。登録が「eBASE → 新商談マスタ」の2段階になり、承認ルートが未定</t>
         </is>
       </c>
       <c r="I10" s="15" t="inlineStr">
@@ -1223,7 +1223,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="98" customHeight="1">
+    <row r="13" ht="112" customHeight="1">
       <c r="B13" s="7" t="n">
         <v>7</v>
       </c>
@@ -1246,7 +1246,7 @@
         <is>
           <t>【登録チーム】製品登録（eBASE・商談システム）
 　← 中間品登録完了
-　→ eBASE：製品登録
+　※eBASEと商談システムに同時に入力
 　→ 商談システム：製品マスタ登録
 　　【承認ルート】品管 ⇒ 商品部本部長</t>
         </is>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>前工程（中間品→製品）のつながりは同じ。登録先が新商談マスタに変わり、承認ルートが未定</t>
+          <t>前工程（中間品→製品）のつながりは同じ。登録が「eBASE → 新商談マスタ」の2段階になり、承認ルートが未定</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1780,7 +1780,9 @@
       </c>
       <c r="E7" s="34" t="inlineStr">
         <is>
-          <t>原材料登録</t>
+          <t>（登録チームが
+商談システムと
+同時に入力）</t>
         </is>
       </c>
       <c r="F7" s="34" t="inlineStr">
@@ -1792,7 +1794,7 @@
       </c>
       <c r="G7" s="34" t="inlineStr">
         <is>
-          <t>本部品管
+          <t>本部品管（eBASE上）
 原材料コード⇔
 eBASEコード紐付け</t>
         </is>
@@ -1822,9 +1824,11 @@
 （eBASE）</t>
         </is>
       </c>
-      <c r="M7" s="34" t="inlineStr">
-        <is>
-          <t>原材料登録</t>
+      <c r="M7" s="36" t="inlineStr">
+        <is>
+          <t>eBASE
+原材料登録
+（先に登録）</t>
         </is>
       </c>
       <c r="N7" s="36" t="inlineStr">
@@ -1910,7 +1914,9 @@
       </c>
       <c r="E9" s="34" t="inlineStr">
         <is>
-          <t>中間品登録</t>
+          <t>（登録チームが
+商談システムと
+同時に入力）</t>
         </is>
       </c>
       <c r="F9" s="34" t="inlineStr">
@@ -1951,9 +1957,11 @@
 （eBASE）</t>
         </is>
       </c>
-      <c r="M9" s="34" t="inlineStr">
-        <is>
-          <t>中間品登録</t>
+      <c r="M9" s="36" t="inlineStr">
+        <is>
+          <t>eBASE
+中間品登録
+（先に登録）</t>
         </is>
       </c>
       <c r="N9" s="36" t="inlineStr">
@@ -2039,7 +2047,9 @@
       </c>
       <c r="E11" s="34" t="inlineStr">
         <is>
-          <t>製品登録</t>
+          <t>（登録チームが
+商談システムと
+同時に入力）</t>
         </is>
       </c>
       <c r="F11" s="34" t="inlineStr">
@@ -2080,9 +2090,11 @@
 （eBASE）</t>
         </is>
       </c>
-      <c r="M11" s="34" t="inlineStr">
-        <is>
-          <t>製品登録</t>
+      <c r="M11" s="36" t="inlineStr">
+        <is>
+          <t>eBASE
+製品登録
+（先に登録）</t>
         </is>
       </c>
       <c r="N11" s="36" t="inlineStr">
@@ -2131,7 +2143,7 @@
     <row r="15">
       <c r="B15" s="44" t="inlineStr">
         <is>
-          <t>2. 変わるのは「登録先（商談システム → 新商談マスタ）」と「承認ルート」。新商談マスタで品管⇒商品部本部長の承認をどうするか決める必要がある。</t>
+          <t>2. 変わるのは登録のやり方。現行は登録チームがeBASE・商談システムに同時入力 → 導入後は「eBASE登録 → 新商談マスタ登録」の2段階。承認ルート（品管⇒商品部本部長）をどうするかも決める必要がある。</t>
         </is>
       </c>
     </row>
